--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45991.60505430448</v>
+        <v>45991.60505430555</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -532,6 +532,1142 @@
       </c>
       <c r="D6" t="n">
         <v>63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45991.61448378472</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45991.61457631944</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45991.61466901621</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45991.61476163194</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45991.61483112269</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45991.61494693287</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45991.61506271991</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45991.61517853009</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45991.61529436342</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45991.61536384259</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45991.61545646991</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45991.61552596065</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45991.61564173611</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45991.61575761574</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45991.61587340278</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45991.61596605324</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45991.61603553241</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45991.61610540509</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45991.61622177083</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45991.61633760417</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45991.61645246528</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45991.61656900463</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45991.61668414352</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45991.61680009259</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>64.09999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45991.61691572917</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D31" t="n">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45991.61703155092</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>60.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45991.6171484838</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45991.61721695602</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45991.61733290509</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45991.61737917824</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45991.61749475695</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>27</v>
+      </c>
+      <c r="D37" t="n">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45991.61765695602</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45991.61772670139</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>28</v>
+      </c>
+      <c r="D39" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45991.61784232639</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45991.61795820602</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45991.61807403935</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45991.61819003472</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45991.61832846064</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45991.61846744213</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45991.61860646991</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45991.61869913194</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D47" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45991.61879178241</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D48" t="n">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45991.61890756944</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45991.61902340277</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45991.61916241898</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45991.61927822917</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45991.61939402778</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45991.61950986111</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45991.61967209491</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>27</v>
+      </c>
+      <c r="D55" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45991.61978792824</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45991.61990385417</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>27</v>
+      </c>
+      <c r="D57" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45991.62002144676</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45991.62011229167</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45991.62022819444</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45991.62034416667</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D61" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45991.62045997685</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45991.62057577547</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D63" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45991.62064520834</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45991.6207146875</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45991.62080733796</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45991.62092321759</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>27</v>
+      </c>
+      <c r="D67" t="n">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45991.62103908565</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45991.62115490741</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>28</v>
+      </c>
+      <c r="D69" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45991.62127075232</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>65.09999999999999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45991.62138657407</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45991.62150243056</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45991.62157268519</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D73" t="n">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45991.62164146991</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45991.62173415509</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D75" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45991.62185005787</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D76" t="n">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45991.62196697944</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>66.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45991.62196697944</v>
+        <v>45991.62196697917</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1668,6 +1668,5158 @@
       </c>
       <c r="D77" t="n">
         <v>66.40000000000001</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45991.6220850463</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>30</v>
+      </c>
+      <c r="D78" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45991.62212975694</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>30</v>
+      </c>
+      <c r="D79" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45991.62224520833</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>30</v>
+      </c>
+      <c r="D80" t="n">
+        <v>67.59999999999999</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45991.62236087963</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D81" t="n">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45991.62247686343</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D82" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45991.62259318287</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>29</v>
+      </c>
+      <c r="D83" t="n">
+        <v>68.09999999999999</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45991.62270947917</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45991.62275373843</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D85" t="n">
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45991.62286958333</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D86" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45991.62298542824</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>30</v>
+      </c>
+      <c r="D87" t="n">
+        <v>75.90000000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45991.62305490741</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D88" t="n">
+        <v>75.09999999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45991.62312457176</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>30</v>
+      </c>
+      <c r="D89" t="n">
+        <v>75.8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45991.62326340278</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D90" t="n">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45991.62337940972</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D91" t="n">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45991.62342557871</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45991.62349509259</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D93" t="n">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45991.62361091435</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D94" t="n">
+        <v>72.8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45991.62372678241</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D95" t="n">
+        <v>77.7</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45991.62384265046</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45991.62398159722</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D97" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45991.62409752315</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D98" t="n">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45991.62421336806</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>79.90000000000001</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45991.62432988426</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D100" t="n">
+        <v>79.7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45991.62449145834</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D101" t="n">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45991.62460741898</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>78.7</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45991.62467704861</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45991.62474653935</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D104" t="n">
+        <v>74.59999999999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45991.62486246528</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D105" t="n">
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45991.62497841435</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D106" t="n">
+        <v>67.09999999999999</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45991.62514010417</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D107" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45991.62530269676</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D108" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45991.62534855324</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D109" t="n">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45991.62544125</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D110" t="n">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45991.62553388889</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>25</v>
+      </c>
+      <c r="D111" t="n">
+        <v>78.90000000000001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45991.62564969908</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>25</v>
+      </c>
+      <c r="D112" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45991.62576554398</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D113" t="n">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45991.6258350463</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="D114" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45991.62606667824</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45991.62611299768</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>23</v>
+      </c>
+      <c r="D116" t="n">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45991.62622886574</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45991.62629836806</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D118" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45991.62641473379</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D119" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45991.62646103009</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D120" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45991.62653048611</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D121" t="n">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45991.62666905093</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D122" t="n">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45991.62676173611</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D123" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45991.62687755787</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D124" t="n">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45991.62699335648</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D125" t="n">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45991.62710920139</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>77.59999999999999</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45991.62722516204</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D127" t="n">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45991.62734079861</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D128" t="n">
+        <v>78.40000000000001</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45991.62745662037</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D129" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45991.62757246528</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D130" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45991.62764193287</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>79.09999999999999</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45991.62775775463</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45991.62787358796</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D133" t="n">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45991.62794309028</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D134" t="n">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45991.62803576389</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D135" t="n">
+        <v>75.09999999999999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45991.6281515625</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D136" t="n">
+        <v>73.90000000000001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45991.62826737268</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>73.59999999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45991.62838318287</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D138" t="n">
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45991.6284990625</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D139" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45991.62861488426</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D140" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45991.62873070602</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D141" t="n">
+        <v>64.59999999999999</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45991.62886969907</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>25</v>
+      </c>
+      <c r="D142" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45991.62898547453</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D143" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45991.62907878472</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>25</v>
+      </c>
+      <c r="D144" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45991.62919538195</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D145" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45991.62926353009</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D146" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45991.62935652778</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D147" t="n">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45991.62942564815</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D148" t="n">
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45991.62949512732</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D149" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45991.62954144676</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D150" t="n">
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45991.62965728009</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45991.62974996528</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D152" t="n">
+        <v>60.2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45991.62988903935</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D153" t="n">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45991.63000493056</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D154" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45991.63012084491</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D155" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45991.63016739584</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D156" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45991.63025965277</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D157" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45991.63035224537</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D158" t="n">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45991.63046807871</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D159" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45991.63058391204</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D160" t="n">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45991.63069979167</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D161" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45991.63076925926</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D162" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45991.63088510417</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>28</v>
+      </c>
+      <c r="D163" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45991.63097774306</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45991.63109368055</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D165" t="n">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45991.63118673611</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45991.63134851852</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>26</v>
+      </c>
+      <c r="D167" t="n">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45991.63151071759</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D168" t="n">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45991.63164972222</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D169" t="n">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45991.63176575232</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>25</v>
+      </c>
+      <c r="D170" t="n">
+        <v>52.7</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45991.63188152778</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D171" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45991.63199756944</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D172" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45991.63206684028</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D173" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45991.6321363426</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>24</v>
+      </c>
+      <c r="D174" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45991.63225215278</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45991.63239118055</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D176" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45991.63253018518</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D177" t="n">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45991.6325765162</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>22</v>
+      </c>
+      <c r="D178" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45991.63264608796</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D179" t="n">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45991.63276209491</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D180" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45991.63283171297</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D181" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45991.63292394676</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D182" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45991.63303980324</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D183" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45991.6331324537</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45991.63322516204</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D185" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45991.63334103009</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D186" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45991.63341056713</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D187" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45991.63348010417</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D188" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45991.63359597222</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D189" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45991.63371181713</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D190" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45991.63380459491</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D191" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45991.63387403935</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>22</v>
+      </c>
+      <c r="D192" t="n">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45991.63396670139</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D193" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45991.63408253472</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D194" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45991.63422150463</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D195" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45991.63433734954</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D196" t="n">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45991.63447642361</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D197" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45991.63459226852</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>20</v>
+      </c>
+      <c r="D198" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45991.63468493056</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45991.63475452546</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D200" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45991.6348934838</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D201" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45991.63493983796</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>20</v>
+      </c>
+      <c r="D202" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45991.63500931713</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>20</v>
+      </c>
+      <c r="D203" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45991.63512516204</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>20</v>
+      </c>
+      <c r="D204" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45991.63524099537</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D205" t="n">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45991.63535685185</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D206" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45991.63544953704</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D207" t="n">
+        <v>51.1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45991.63551925926</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D208" t="n">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45991.6356118287</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D209" t="n">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45991.63572777778</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D210" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45991.6358434838</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D211" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45991.63595934028</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45991.63607517361</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D213" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45991.63612148148</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D214" t="n">
+        <v>52.4</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45991.63619122685</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D215" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45991.63630782408</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="D216" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45991.63642260417</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D217" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45991.6365853588</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>22</v>
+      </c>
+      <c r="D218" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45991.63667746528</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D219" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45991.63679334491</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D220" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45991.63690924768</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D221" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45991.63700193287</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D222" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45991.63707143519</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D223" t="n">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45991.63711777778</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>25</v>
+      </c>
+      <c r="D224" t="n">
+        <v>54.3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45991.63718736111</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>25</v>
+      </c>
+      <c r="D225" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45991.63728005787</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D226" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>45991.63734960648</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D227" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45991.63746613426</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45991.63758126157</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D229" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45991.63762756944</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D230" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45991.6377434375</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D231" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45991.63781320602</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D232" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45991.63790590277</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D233" t="n">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45991.63804457176</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D234" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45991.63818365741</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D235" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45991.63823002315</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D236" t="n">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45991.63834582176</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D237" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>45991.63841532407</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D238" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>45991.63853288195</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D239" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>45991.63864701389</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D240" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>45991.63869496528</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D241" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>45991.63878611111</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>25</v>
+      </c>
+      <c r="D242" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>45991.6389718287</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D243" t="n">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>45991.6390410301</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D244" t="n">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>45991.63915685185</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D245" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>45991.63927277778</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D246" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>45991.63941177083</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D247" t="n">
+        <v>64.59999999999999</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>45991.63945813657</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D248" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>45991.63955084491</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D249" t="n">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>45991.63966672454</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D250" t="n">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>45991.63973622685</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D251" t="n">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>45991.63980578704</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>45991.63989847223</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>23</v>
+      </c>
+      <c r="D253" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>45991.64001439814</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="D254" t="n">
+        <v>71.40000000000001</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>45991.6401319213</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="D255" t="n">
+        <v>70.09999999999999</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>45991.64024752315</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D256" t="n">
+        <v>67.59999999999999</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>45991.64033880787</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D257" t="n">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>45991.64040840277</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D258" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>45991.64052424768</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D259" t="n">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>45991.6406402662</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D260" t="n">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>45991.64073291667</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D261" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>45991.64084891204</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D262" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>45991.64091855324</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D263" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>45991.64103445602</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D264" t="n">
+        <v>61.7</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>45991.64122006945</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D265" t="n">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>45991.64131230324</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D266" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>45991.64135864584</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D267" t="n">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>45991.64147449074</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D268" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>45991.6415904051</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D269" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>45991.64170626157</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D270" t="n">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>45991.6418684838</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D271" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>45991.64193806713</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>30</v>
+      </c>
+      <c r="D272" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>45991.64198442129</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D273" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>45991.64207694444</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>30</v>
+      </c>
+      <c r="D274" t="n">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>45991.64214649305</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>30</v>
+      </c>
+      <c r="D275" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>45991.64223922454</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>30</v>
+      </c>
+      <c r="D276" t="n">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>45991.64242457176</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D277" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>45991.64258680555</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D278" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>45991.64267956019</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D279" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>45991.64286484953</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D280" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>45991.6429807176</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D281" t="n">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>45991.64309664352</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D282" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>45991.64316615741</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D283" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>45991.64328217592</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D284" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>45991.64342136574</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D285" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>45991.64353721065</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D286" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>45991.64372270833</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D287" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>45991.64383863426</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D288" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>45991.64390854166</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D289" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>45991.64395450232</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D290" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>45991.64407130787</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D291" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>45991.64416298611</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D292" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>45991.6442325</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D293" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>45991.64434840278</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D294" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>45991.64446421296</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>26</v>
+      </c>
+      <c r="D295" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>45991.64458008102</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D296" t="n">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>45991.64469631945</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D297" t="n">
+        <v>69.40000000000001</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>45991.64474226852</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D298" t="n">
+        <v>64.40000000000001</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>45991.64481366898</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>24</v>
+      </c>
+      <c r="D299" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>45991.64492766204</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D300" t="n">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>45991.64502041667</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>25</v>
+      </c>
+      <c r="D301" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>45991.64509008102</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D302" t="n">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>45991.64515949074</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>25</v>
+      </c>
+      <c r="D303" t="n">
+        <v>64.40000000000001</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>45991.64520627315</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>25</v>
+      </c>
+      <c r="D304" t="n">
+        <v>65.09999999999999</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>45991.6452755787</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>26</v>
+      </c>
+      <c r="D305" t="n">
+        <v>64.09999999999999</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>45991.64553035879</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D306" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>45991.64557673611</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D307" t="n">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>45991.64576241898</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D308" t="n">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>45991.64590164352</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D309" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>45991.64597098379</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D310" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>45991.64606366898</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D311" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>45991.64615635417</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D312" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>45991.64627219908</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D313" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>45991.64638804398</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D314" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>45991.64652743055</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D315" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>45991.64662011574</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D316" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>45991.64673627315</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D317" t="n">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>45991.64689868056</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D318" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>45991.64696797454</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D319" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>45991.64710700232</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D320" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>45991.64722314815</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D321" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>45991.64733876158</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D322" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>45991.64745655093</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>23</v>
+      </c>
+      <c r="D323" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>45991.6474780787</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>23</v>
+      </c>
+      <c r="D324" t="n">
+        <v>44.6</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>45991.64761704861</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D325" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>45991.64773300926</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D326" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>45991.64782586806</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D327" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>45991.64789554398</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D328" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>45991.64794188657</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="D329" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>45991.64803459491</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D330" t="n">
+        <v>45.4</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n">
+        <v>45991.64817388889</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>23</v>
+      </c>
+      <c r="D331" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n">
+        <v>45991.64828972222</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D332" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n">
+        <v>45991.64840575231</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D333" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n">
+        <v>45991.6485447801</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D334" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n">
+        <v>45991.64861428241</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>22</v>
+      </c>
+      <c r="D335" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="n">
+        <v>45991.64873020833</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D336" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="n">
+        <v>45991.64877662037</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D337" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="n">
+        <v>45991.64889244213</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D338" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>45991.64896207176</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D339" t="n">
+        <v>45.4</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n">
+        <v>45991.6490547338</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D340" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="n">
+        <v>45991.64917075232</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D341" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45991.649333125</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D342" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="n">
+        <v>45991.64940269676</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D343" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="n">
+        <v>45991.64947229167</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D344" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="n">
+        <v>45991.64958804398</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D345" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="n">
+        <v>45991.64970398148</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D346" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="n">
+        <v>45991.64981988426</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D347" t="n">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="n">
+        <v>45991.64998278935</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D348" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="n">
+        <v>45991.65014465278</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D349" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="n">
+        <v>45991.65021496528</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>21</v>
+      </c>
+      <c r="D350" t="n">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="n">
+        <v>45991.65026041667</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D351" t="n">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="n">
+        <v>45991.65039958333</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D352" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="n">
+        <v>45991.65051552084</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D353" t="n">
+        <v>51.1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="n">
+        <v>45991.65063128472</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D354" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="n">
+        <v>45991.65074766204</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D355" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="n">
+        <v>45991.65086315972</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="D356" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="n">
+        <v>45991.65097936342</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D357" t="n">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="n">
+        <v>45991.65109540509</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D358" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="n">
+        <v>45991.65123451389</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D359" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="n">
+        <v>45991.65135048611</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D360" t="n">
+        <v>46.7</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="n">
+        <v>45991.65146609954</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D361" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>45991.65162862268</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D362" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n">
+        <v>45991.65183724537</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="D363" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n">
+        <v>45991.65195315972</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D364" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n">
+        <v>45991.65206909722</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D365" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="n">
+        <v>45991.65218501158</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D366" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="n">
+        <v>45991.65227765046</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D367" t="n">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n">
+        <v>45991.65239358796</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D368" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n">
+        <v>45991.6524399537</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D369" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n">
+        <v>45991.65253273148</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D370" t="n">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n">
+        <v>45991.65260224537</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D371" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n">
+        <v>45991.65269503473</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D372" t="n">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>45991.65276461805</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D373" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>45991.65295011574</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D374" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n">
+        <v>45991.65299642361</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>22</v>
+      </c>
+      <c r="D375" t="n">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="n">
+        <v>45991.65313579861</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>22</v>
+      </c>
+      <c r="D376" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="n">
+        <v>45991.65318199074</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D377" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n">
+        <v>45991.65332112269</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D378" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="n">
+        <v>45991.65343693287</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D379" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>45991.65352974537</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D380" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>45991.65366884259</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D381" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>45991.6538312037</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D382" t="n">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>45991.65392390046</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D383" t="n">
+        <v>44.3</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>45991.65399344907</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D384" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>45991.65408831018</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D385" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>45991.65424827546</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>20</v>
+      </c>
+      <c r="D386" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>45991.65441077546</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D387" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>45991.65450359954</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D388" t="n">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>45991.65461975695</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>21</v>
+      </c>
+      <c r="D389" t="n">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>45991.65473553241</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D390" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>45991.6548515625</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D391" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>45991.65492111111</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D392" t="n">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>45991.65503706018</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D393" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>45991.65510668982</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="D394" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>45991.65519953704</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D395" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>45991.65529251158</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="D396" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>45991.65543175926</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D397" t="n">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>45991.655524375</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D398" t="n">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>45991.65564042907</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D399" t="n">
+        <v>53.8</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D399"/>
+  <dimension ref="A1:D400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6808,7 +6808,7 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
-        <v>45991.65564042907</v>
+        <v>45991.65564042824</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -6820,6 +6820,22 @@
       </c>
       <c r="D399" t="n">
         <v>53.8</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>45991.6557100731</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D400" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D400"/>
+  <dimension ref="A1:D401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6824,7 +6824,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
-        <v>45991.6557100731</v>
+        <v>45991.65571006944</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -6836,6 +6836,22 @@
       </c>
       <c r="D400" t="n">
         <v>55</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>45991.65589566527</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D401" t="n">
+        <v>57.6</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D401"/>
+  <dimension ref="A1:D403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,7 +6840,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
-        <v>45991.65589566527</v>
+        <v>45991.65589565972</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -6852,6 +6852,38 @@
       </c>
       <c r="D401" t="n">
         <v>57.6</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>45991.65601143519</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D402" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>45991.65605775797</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D403" t="n">
+        <v>59.8</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D403"/>
+  <dimension ref="A1:D406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6872,7 +6872,7 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
-        <v>45991.65605775797</v>
+        <v>45991.65605775463</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -6884,6 +6884,54 @@
       </c>
       <c r="D403" t="n">
         <v>59.8</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>45991.65617369213</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D404" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>45991.65626636574</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D405" t="n">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>45991.65633597606</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D406" t="n">
+        <v>58.1</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D406"/>
+  <dimension ref="A1:D408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6920,7 +6920,7 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
-        <v>45991.65633597606</v>
+        <v>45991.65633597222</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -6932,6 +6932,38 @@
       </c>
       <c r="D406" t="n">
         <v>58.1</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>45991.65642868056</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D407" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>45991.65649826003</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D408" t="n">
+        <v>55.6</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D408"/>
+  <dimension ref="A1:D410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6952,7 +6952,7 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
-        <v>45991.65649826003</v>
+        <v>45991.65649826389</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -6964,6 +6964,38 @@
       </c>
       <c r="D408" t="n">
         <v>55.6</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>45991.65659087963</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D409" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>45991.65670680122</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D410" t="n">
+        <v>57.5</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D410"/>
+  <dimension ref="A1:D425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6984,7 +6984,7 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
-        <v>45991.65670680122</v>
+        <v>45991.65670680555</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -6996,6 +6996,246 @@
       </c>
       <c r="D410" t="n">
         <v>57.5</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>45991.65682292824</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D411" t="n">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>45991.65693866898</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D412" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>45991.65698498843</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D413" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>45991.65707872685</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D414" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>45991.65714728009</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D415" t="n">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>45991.65726354167</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D416" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>45991.6574022338</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D417" t="n">
+        <v>66.09999999999999</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>45991.6574949537</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D418" t="n">
+        <v>67.3</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>45991.65756454861</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D419" t="n">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>45991.65765726852</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D420" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>45991.6577500463</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D421" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>45991.65786603009</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D422" t="n">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>45991.65791238426</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D423" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>45991.65802832176</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D424" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>45991.65814417315</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D425" t="n">
+        <v>66.3</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D425"/>
+  <dimension ref="A1:D427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7224,7 +7224,7 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
-        <v>45991.65814417315</v>
+        <v>45991.65814417824</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -7236,6 +7236,38 @@
       </c>
       <c r="D425" t="n">
         <v>66.3</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>45991.65821369213</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D426" t="n">
+        <v>68.7</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>45991.65826036019</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D427" t="n">
+        <v>66.8</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D427"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7256,7 +7256,7 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
-        <v>45991.65826036019</v>
+        <v>45991.6582603588</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -7268,6 +7268,54 @@
       </c>
       <c r="D427" t="n">
         <v>66.8</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>45991.65837599537</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D428" t="n">
+        <v>68.2</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>45991.65846878472</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D429" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>45991.65856149373</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D430" t="n">
+        <v>72.09999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D430"/>
+  <dimension ref="A1:D436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7304,7 +7304,7 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
-        <v>45991.65856149373</v>
+        <v>45991.65856149306</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -7316,6 +7316,102 @@
       </c>
       <c r="D430" t="n">
         <v>72.09999999999999</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>45991.65870068287</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D431" t="n">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>45991.65879358797</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D432" t="n">
+        <v>70.90000000000001</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>45991.65888636574</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>27</v>
+      </c>
+      <c r="D433" t="n">
+        <v>69.7</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>45991.65900221065</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D434" t="n">
+        <v>67.40000000000001</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>45991.6590952662</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D435" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>45991.65921135573</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D436" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D436"/>
+  <dimension ref="A1:D442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7400,7 +7400,7 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>45991.65921135573</v>
+        <v>45991.65921135417</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -7412,6 +7412,102 @@
       </c>
       <c r="D436" t="n">
         <v>68</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>45991.65928072917</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D437" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>45991.65937363426</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D438" t="n">
+        <v>65.90000000000001</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>45991.65948902778</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D439" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>45991.65960506944</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D440" t="n">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>45991.65972082176</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D441" t="n">
+        <v>64.09999999999999</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>45991.65983686816</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D442" t="n">
+        <v>63.4</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D442"/>
+  <dimension ref="A1:D520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7496,7 +7496,7 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
-        <v>45991.65983686816</v>
+        <v>45991.65983686343</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -7508,6 +7508,1254 @@
       </c>
       <c r="D442" t="n">
         <v>63.4</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>45991.6599299537</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D443" t="n">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>45991.66004585648</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D444" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>45991.66016130787</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D445" t="n">
+        <v>67.3</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>45991.66025415509</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D446" t="n">
+        <v>67.40000000000001</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>45991.66032408565</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D447" t="n">
+        <v>64.90000000000001</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>45991.66041657407</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D448" t="n">
+        <v>63.9</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>45991.66057873843</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D449" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>45991.66071778935</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D450" t="n">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>45991.66083364583</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D451" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>45991.66099599537</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D452" t="n">
+        <v>68.09999999999999</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>45991.66106563657</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D453" t="n">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>45991.66120488426</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D454" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>45991.66132074074</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D455" t="n">
+        <v>71.09999999999999</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>45991.66141342593</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D456" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n">
+        <v>45991.66152928241</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D457" t="n">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n">
+        <v>45991.66159887731</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D458" t="n">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n">
+        <v>45991.66171490741</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D459" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n">
+        <v>45991.66185399306</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D460" t="n">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n">
+        <v>45991.66196991898</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="D461" t="n">
+        <v>71.09999999999999</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n">
+        <v>45991.66208574074</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D462" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n">
+        <v>45991.66215530092</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D463" t="n">
+        <v>68.09999999999999</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n">
+        <v>45991.66227118055</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D464" t="n">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n">
+        <v>45991.66238696759</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>26</v>
+      </c>
+      <c r="D465" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n">
+        <v>45991.66247986111</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D466" t="n">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n">
+        <v>45991.66259575231</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D467" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n">
+        <v>45991.66264215278</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D468" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n">
+        <v>45991.66271335648</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D469" t="n">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="n">
+        <v>45991.66282755787</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D470" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="n">
+        <v>45991.66292027778</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D471" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="n">
+        <v>45991.66298979166</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D472" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="n">
+        <v>45991.66310571759</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D473" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="n">
+        <v>45991.66319840278</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D474" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="n">
+        <v>45991.66331434028</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D475" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="n">
+        <v>45991.66343071759</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D476" t="n">
+        <v>60.2</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="n">
+        <v>45991.66352295139</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D477" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="n">
+        <v>45991.66366211806</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>25</v>
+      </c>
+      <c r="D478" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="n">
+        <v>45991.66375498843</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D479" t="n">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="n">
+        <v>45991.6639171875</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D480" t="n">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="n">
+        <v>45991.66407950231</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D481" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="n">
+        <v>45991.66424172454</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D482" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="n">
+        <v>45991.66435769676</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D483" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="n">
+        <v>45991.66447357639</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D484" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="n">
+        <v>45991.66458944444</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D485" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="n">
+        <v>45991.66475181713</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D486" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="n">
+        <v>45991.66496048611</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D487" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="n">
+        <v>45991.66509973379</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D488" t="n">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="n">
+        <v>45991.665169375</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D489" t="n">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="n">
+        <v>45991.66528534722</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D490" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="n">
+        <v>45991.66537791667</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D491" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="n">
+        <v>45991.66544738426</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D492" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="n">
+        <v>45991.66551706019</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D493" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="n">
+        <v>45991.66560976852</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D494" t="n">
+        <v>60.2</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="n">
+        <v>45991.66570248843</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>26</v>
+      </c>
+      <c r="D495" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="n">
+        <v>45991.66579519676</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D496" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="n">
+        <v>45991.66591109954</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D497" t="n">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="n">
+        <v>45991.66600380787</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>27</v>
+      </c>
+      <c r="D498" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="n">
+        <v>45991.66607334491</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D499" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="n">
+        <v>45991.6661893287</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D500" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="n">
+        <v>45991.66630604167</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D501" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>45991.66642163195</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D502" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>45991.66646741898</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D503" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="n">
+        <v>45991.66653758102</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D504" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="n">
+        <v>45991.66658329861</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D505" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="n">
+        <v>45991.66665395833</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D506" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="n">
+        <v>45991.66669917824</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D507" t="n">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="n">
+        <v>45991.66677344908</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D508" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="n">
+        <v>45991.66688671296</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="D509" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="n">
+        <v>45991.66704704861</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D510" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
+        <v>45991.66711649305</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D511" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>45991.66720921297</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>23</v>
+      </c>
+      <c r="D512" t="n">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="n">
+        <v>45991.66732662037</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D513" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>45991.66741793982</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D514" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>45991.6675337963</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D515" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="n">
+        <v>45991.66764979166</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>26</v>
+      </c>
+      <c r="D516" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="n">
+        <v>45991.66776575232</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D517" t="n">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="n">
+        <v>45991.66792820602</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D518" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="n">
+        <v>45991.66804413195</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D519" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="n">
+        <v>45991.66813679436</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D520" t="n">
+        <v>56.4</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D520"/>
+  <dimension ref="A1:D545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8744,7 +8744,7 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
-        <v>45991.66813679436</v>
+        <v>45991.66813679398</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -8756,6 +8756,406 @@
       </c>
       <c r="D520" t="n">
         <v>56.4</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="n">
+        <v>45991.66830145833</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D521" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="n">
+        <v>45991.66834789352</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D522" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="n">
+        <v>45991.66848688657</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D523" t="n">
+        <v>54.3</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="n">
+        <v>45991.66860282407</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D524" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="n">
+        <v>45991.66867236111</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D525" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="n">
+        <v>45991.66876506944</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D526" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="n">
+        <v>45991.66883458333</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D527" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="n">
+        <v>45991.66892738426</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="D528" t="n">
+        <v>45.9</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="n">
+        <v>45991.66904327546</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D529" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="n">
+        <v>45991.66915928241</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D530" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="n">
+        <v>45991.66927511574</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D531" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="n">
+        <v>45991.66939107639</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>26</v>
+      </c>
+      <c r="D532" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="n">
+        <v>45991.66950756944</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D533" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="n">
+        <v>45991.66957663195</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D534" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="n">
+        <v>45991.66973890046</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D535" t="n">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="n">
+        <v>45991.66985481481</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D536" t="n">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>45991.66997077546</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>25</v>
+      </c>
+      <c r="D537" t="n">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>45991.67008665509</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D538" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="n">
+        <v>45991.67015620371</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D539" t="n">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="n">
+        <v>45991.67022599537</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D540" t="n">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="n">
+        <v>45991.67027268519</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D541" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="n">
+        <v>45991.67034215278</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D542" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="n">
+        <v>45991.67041118055</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D543" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="n">
+        <v>45991.67052703704</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D544" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="n">
+        <v>45991.67066606761</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D545" t="n">
+        <v>58.5</v>
       </c>
     </row>
   </sheetData>

--- a/lesson 6/sensor_data_20251130.xlsx
+++ b/lesson 6/sensor_data_20251130.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D545"/>
+  <dimension ref="A1:D559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9144,7 +9144,7 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
-        <v>45991.67066606761</v>
+        <v>45991.67066606481</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -9156,6 +9156,230 @@
       </c>
       <c r="D545" t="n">
         <v>58.5</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="n">
+        <v>45991.6707587963</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D546" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="n">
+        <v>45991.67082829861</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D547" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="n">
+        <v>45991.6708746412</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D548" t="n">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="n">
+        <v>45991.67099048611</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>26</v>
+      </c>
+      <c r="D549" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="n">
+        <v>45991.67103890047</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D550" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="n">
+        <v>45991.67110737268</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D551" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="n">
+        <v>45991.67119934028</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D552" t="n">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="n">
+        <v>45991.67126883102</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D553" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="n">
+        <v>45991.67131524305</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D554" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="n">
+        <v>45991.67140821759</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D555" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="n">
+        <v>45991.67147778935</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D556" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="n">
+        <v>45991.67166278935</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D557" t="n">
+        <v>56.6</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="n">
+        <v>45991.67175571759</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D558" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="n">
+        <v>45991.67192846487</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D559" t="n">
+        <v>56.2</v>
       </c>
     </row>
   </sheetData>
